--- a/org/sabae-jinko.files/chikubetsu-jinko-setaisuR8-4.xlsx
+++ b/org/sabae-jinko.files/chikubetsu-jinko-setaisuR8-4.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\fs\Docs_2026\DX\34_統計\06_ホームページ\R8.4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F84F7767-3A03-4428-9730-FD69AF167466}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F65EF837-EA8F-4B10-8A3F-E6BDE12BFBB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="949" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1697,16 +1697,16 @@
         <v>6</v>
       </c>
       <c r="J6" s="79">
-        <v>3868</v>
+        <v>3757</v>
       </c>
       <c r="K6" s="79">
-        <v>4996</v>
+        <v>4822</v>
       </c>
       <c r="L6" s="79">
-        <v>5080</v>
+        <v>4922</v>
       </c>
       <c r="M6" s="80">
-        <v>10076</v>
+        <v>9744</v>
       </c>
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="18.75" customHeight="1">
@@ -1735,16 +1735,16 @@
         <v>8</v>
       </c>
       <c r="J7" s="79">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="K7" s="79">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="L7" s="79">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="M7" s="80">
-        <v>208</v>
+        <v>198</v>
       </c>
     </row>
     <row r="8" spans="1:14" s="1" customFormat="1" ht="18.75" customHeight="1">
@@ -1763,7 +1763,7 @@
         <v>50</v>
       </c>
       <c r="J8" s="79">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="K8" s="84"/>
       <c r="L8" s="84"/>
@@ -1791,16 +1791,16 @@
         <v>10</v>
       </c>
       <c r="J9" s="80">
-        <v>4052</v>
+        <v>3933</v>
       </c>
       <c r="K9" s="80">
-        <v>5109</v>
+        <v>4928</v>
       </c>
       <c r="L9" s="80">
-        <v>5175</v>
+        <v>5014</v>
       </c>
       <c r="M9" s="80">
-        <v>10284</v>
+        <v>9942</v>
       </c>
     </row>
     <row r="10" spans="1:14" s="1" customFormat="1" ht="18.75" customHeight="1">
@@ -1937,16 +1937,16 @@
         <v>6</v>
       </c>
       <c r="C14" s="79">
-        <v>5961</v>
+        <v>6072</v>
       </c>
       <c r="D14" s="79">
-        <v>7268</v>
+        <v>7442</v>
       </c>
       <c r="E14" s="79">
-        <v>7676</v>
+        <v>7834</v>
       </c>
       <c r="F14" s="80">
-        <v>14944</v>
+        <v>15276</v>
       </c>
       <c r="H14" s="4"/>
       <c r="I14" s="9" t="s">
@@ -1973,16 +1973,16 @@
         <v>8</v>
       </c>
       <c r="C15" s="79">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="D15" s="79">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="E15" s="79">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="F15" s="80">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="H15" s="10" t="s">
         <v>14</v>
@@ -2010,7 +2010,7 @@
         <v>50</v>
       </c>
       <c r="C16" s="79">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D16" s="84"/>
       <c r="E16" s="84"/>
@@ -2033,16 +2033,16 @@
         <v>10</v>
       </c>
       <c r="C17" s="80">
-        <v>6299</v>
+        <v>6418</v>
       </c>
       <c r="D17" s="80">
-        <v>7518</v>
+        <v>7699</v>
       </c>
       <c r="E17" s="80">
-        <v>7850</v>
+        <v>8011</v>
       </c>
       <c r="F17" s="80">
-        <v>15368</v>
+        <v>15710</v>
       </c>
       <c r="H17" s="11"/>
       <c r="I17" s="9" t="s">
